--- a/datos-referencia/recetas.xlsx
+++ b/datos-referencia/recetas.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recetas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,283 +413,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>id_receta</t>
+          <t>plato</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>nombre</t>
+          <t>ingrediente</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>categoria</t>
+          <t>cantidad</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>precio_venta</t>
+          <t>unidad</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>ingredientes_json</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>REC001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Paella de Marisco</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Arroces</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>[{"ingrediente":"Arroz","cantidad":0.15,"unidad":"kg","coste_unitario":1.20},{"ingrediente":"Gambas","cantidad":0.12,"unidad":"kg","coste_unitario":12.00},{"ingrediente":"Mejillones","cantidad":0.10,"unidad":"kg","coste_unitario":4.50},{"ingrediente":"Caldo Pescado","cantidad":0.30,"unidad":"l","coste_unitario":0.80},{"ingrediente":"Aceite Oliva","cantidad":0.02,"unidad":"l","coste_unitario":3.50}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>REC002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Chuletón de Ternera</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Carnes</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>32</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>[{"ingrediente":"Ternera Chuleton","cantidad":0.35,"unidad":"kg","coste_unitario":22.00},{"ingrediente":"Patatas","cantidad":0.20,"unidad":"kg","coste_unitario":0.60},{"ingrediente":"Sal","cantidad":0.005,"unidad":"kg","coste_unitario":0.50},{"ingrediente":"Aceite Oliva","cantidad":0.01,"unidad":"l","coste_unitario":3.50}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>REC003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Gazpacho</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Sopas Frías</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>[{"ingrediente":"Tomate","cantidad":0.30,"unidad":"kg","coste_unitario":1.80},{"ingrediente":"Pepino","cantidad":0.05,"unidad":"kg","coste_unitario":1.20},{"ingrediente":"Pimiento","cantidad":0.04,"unidad":"kg","coste_unitario":1.50},{"ingrediente":"Pan","cantidad":0.03,"unidad":"kg","coste_unitario":2.00},{"ingrediente":"Aceite Oliva","cantidad":0.02,"unidad":"l","coste_unitario":3.50}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>REC004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Crema Catalana</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Postres</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>[{"ingrediente":"Nata","cantidad":0.15,"unidad":"l","coste_unitario":2.20},{"ingrediente":"Leche","cantidad":0.10,"unidad":"l","coste_unitario":0.90},{"ingrediente":"Huevos","cantidad":0.10,"unidad":"kg","coste_unitario":2.80},{"ingrediente":"Azucar","cantidad":0.04,"unidad":"kg","coste_unitario":1.10}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>REC005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Gin Tonic Premium</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bebidas</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>12</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>[{"ingrediente":"Ginebra Premium","cantidad":0.05,"unidad":"l","coste_unitario":28.00},{"ingrediente":"Tonica","cantidad":0.20,"unidad":"l","coste_unitario":1.80},{"ingrediente":"Limon","cantidad":0.02,"unidad":"kg","coste_unitario":1.50}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>REC006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Ensalada César</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ensaladas</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>[{"ingrediente":"Lechuga","cantidad":0.12,"unidad":"kg","coste_unitario":1.40},{"ingrediente":"Pollo","cantidad":0.10,"unidad":"kg","coste_unitario":6.50},{"ingrediente":"Parmesano","cantidad":0.03,"unidad":"kg","coste_unitario":18.00},{"ingrediente":"Pan","cantidad":0.04,"unidad":"kg","coste_unitario":2.00}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>REC007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Lubina a la Sal</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Pescados</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>28</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>[{"ingrediente":"Lubina","cantidad":0.40,"unidad":"kg","coste_unitario":14.00},{"ingrediente":"Sal Gorda","cantidad":0.50,"unidad":"kg","coste_unitario":0.40},{"ingrediente":"Aceite Oliva","cantidad":0.02,"unidad":"l","coste_unitario":3.50}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>REC008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Tarta de Queso</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Postres</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>[{"ingrediente":"Queso Crema","cantidad":0.15,"unidad":"kg","coste_unitario":5.50},{"ingrediente":"Nata","cantidad":0.08,"unidad":"l","coste_unitario":2.20},{"ingrediente":"Huevos","cantidad":0.06,"unidad":"kg","coste_unitario":2.80},{"ingrediente":"Azucar","cantidad":0.05,"unidad":"kg","coste_unitario":1.10},{"ingrediente":"Galletas","cantidad":0.06,"unidad":"kg","coste_unitario":3.20}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>REC009</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Vino Tinto Copa</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Bebidas</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>[{"ingrediente":"Vino Tinto","cantidad":0.15,"unidad":"l","coste_unitario":6.00}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>REC010</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Agua Mineral</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Bebidas</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>[{"ingrediente":"Agua Mineral","cantidad":0.50,"unidad":"l","coste_unitario":0.35}]</t>
+          <t>coste_kg</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>coste_total</t>
         </is>
       </c>
     </row>

--- a/datos-referencia/recetas.xlsx
+++ b/datos-referencia/recetas.xlsx
@@ -413,39 +413,321 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>id_receta</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>plato</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>ingrediente</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>cantidad</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>unidad</t>
-        </is>
-      </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>cantidad_kg</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>coste_kg</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>coste_total</t>
         </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>coste_teorico</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>R001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Lubina a la Sal</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Pescados</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Ingredientes Lubina a la Sal</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>18</v>
+      </c>
+      <c r="G2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H2" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>R002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Entrecot Premium</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Carnes</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Ingredientes Entrecot Premium</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>R003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Risotto Trufa</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Pastas</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Ingredientes Risotto Trufa</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ensalada César</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Entrantes</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Ingredientes Ensalada César</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>R005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tarta Chocolate</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Postres</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ingredientes Tarta Chocolate</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Paella Mixta</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Arroces</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Ingredientes Paella Mixta</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>11</v>
+      </c>
+      <c r="G7" t="n">
+        <v>11</v>
+      </c>
+      <c r="H7" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>R007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sopa de Marisco</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Sopas</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Ingredientes Sopa de Marisco</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>R008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Hamburguesa Gourmet</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Carnes</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Ingredientes Hamburguesa Gourmet</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>

--- a/datos-referencia/recetas.xlsx
+++ b/datos-referencia/recetas.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recetas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>plato</t>
+          <t>nombre</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -434,27 +434,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>ingrediente</t>
+          <t>precio_venta</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>cantidad_kg</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>coste_kg</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>coste_total</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>coste_teorico</t>
+          <t>ingredientes_json</t>
         </is>
       </c>
     </row>
@@ -474,22 +459,13 @@
           <t>Pescados</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Ingredientes Lubina a la Sal</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>18</v>
-      </c>
-      <c r="G2" t="n">
-        <v>18</v>
-      </c>
-      <c r="H2" t="n">
-        <v>18</v>
+      <c r="D2" t="n">
+        <v>42</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>[{"ingrediente": "Lubina fresca", "cantidad": 0.4, "coste_unitario": 18.0}, {"ingrediente": "Sal marina", "cantidad": 0.5, "coste_unitario": 1.2}, {"ingrediente": "Aceite oliva", "cantidad": 0.05, "coste_unitario": 8.0}]</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -508,22 +484,13 @@
           <t>Carnes</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Ingredientes Entrecot Premium</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="H3" t="n">
-        <v>14.5</v>
+      <c r="D3" t="n">
+        <v>38</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>[{"ingrediente": "Entrecot", "cantidad": 0.35, "coste_unitario": 22.0}, {"ingrediente": "Patata", "cantidad": 0.2, "coste_unitario": 1.5}, {"ingrediente": "Mantequilla", "cantidad": 0.03, "coste_unitario": 9.0}]</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -539,25 +506,16 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pastas</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Ingredientes Risotto Trufa</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="G4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="H4" t="n">
-        <v>8.199999999999999</v>
+          <t>Arroces</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>28</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>[{"ingrediente": "Arroz bomba", "cantidad": 0.1, "coste_unitario": 3.2}, {"ingrediente": "Trufa negra", "cantidad": 0.01, "coste_unitario": 180.0}, {"ingrediente": "Parmesano", "cantidad": 0.05, "coste_unitario": 15.0}]</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -576,22 +534,13 @@
           <t>Entrantes</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Ingredientes Ensalada César</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4.5</v>
+      <c r="D5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>[{"ingrediente": "Lechuga", "cantidad": 0.15, "coste_unitario": 2.0}, {"ingrediente": "Pollo", "cantidad": 0.1, "coste_unitario": 6.5}, {"ingrediente": "Parmesano", "cantidad": 0.03, "coste_unitario": 15.0}]</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -610,22 +559,13 @@
           <t>Postres</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Ingredientes Tarta Chocolate</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3.8</v>
+      <c r="D6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>[{"ingrediente": "Chocolate 70%", "cantidad": 0.08, "coste_unitario": 12.0}, {"ingrediente": "Harina", "cantidad": 0.05, "coste_unitario": 1.0}, {"ingrediente": "Huevo", "cantidad": 0.1, "coste_unitario": 3.0}]</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -644,22 +584,13 @@
           <t>Arroces</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Ingredientes Paella Mixta</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>11</v>
-      </c>
-      <c r="G7" t="n">
-        <v>11</v>
-      </c>
-      <c r="H7" t="n">
-        <v>11</v>
+      <c r="D7" t="n">
+        <v>32</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>[{"ingrediente": "Arroz bomba", "cantidad": 0.12, "coste_unitario": 3.2}, {"ingrediente": "Marisco", "cantidad": 0.15, "coste_unitario": 14.0}, {"ingrediente": "Pollo", "cantidad": 0.1, "coste_unitario": 6.5}]</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -678,22 +609,13 @@
           <t>Sopas</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Ingredientes Sopa de Marisco</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>9.5</v>
+      <c r="D8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>[{"ingrediente": "Marisco", "cantidad": 0.2, "coste_unitario": 14.0}, {"ingrediente": "Tomate", "cantidad": 0.1, "coste_unitario": 2.5}]</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -712,22 +634,13 @@
           <t>Carnes</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Ingredientes Hamburguesa Gourmet</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H9" t="n">
-        <v>7.2</v>
+      <c r="D9" t="n">
+        <v>19</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>[{"ingrediente": "Carne picada", "cantidad": 0.2, "coste_unitario": 9.5}, {"ingrediente": "Pan brioche", "cantidad": 0.08, "coste_unitario": 3.0}, {"ingrediente": "Queso", "cantidad": 0.03, "coste_unitario": 12.0}]</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/datos-referencia/recetas.xlsx
+++ b/datos-referencia/recetas.xlsx
@@ -1,40 +1,66 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recetas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+  <si>
+    <t>id_receta</t>
+  </si>
+  <si>
+    <t>nombre</t>
+  </si>
+  <si>
+    <t>categoria</t>
+  </si>
+  <si>
+    <t>precio_venta</t>
+  </si>
+  <si>
+    <t>ingredientes_json</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +68,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,242 +385,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id_receta</t>
-        </is>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>nombre</t>
-        </is>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>categoria</t>
-        </is>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>precio_venta</t>
-        </is>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>ingredientes_json</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>R001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Lubina a la Sal</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Pescados</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>42</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>[{"ingrediente": "Lubina fresca", "cantidad": 0.4, "coste_unitario": 18.0}, {"ingrediente": "Sal marina", "cantidad": 0.5, "coste_unitario": 1.2}, {"ingrediente": "Aceite oliva", "cantidad": 0.05, "coste_unitario": 8.0}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>R002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Entrecot Premium</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Carnes</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>38</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>[{"ingrediente": "Entrecot", "cantidad": 0.35, "coste_unitario": 22.0}, {"ingrediente": "Patata", "cantidad": 0.2, "coste_unitario": 1.5}, {"ingrediente": "Mantequilla", "cantidad": 0.03, "coste_unitario": 9.0}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>R003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Risotto Trufa</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Arroces</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>28</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>[{"ingrediente": "Arroz bomba", "cantidad": 0.1, "coste_unitario": 3.2}, {"ingrediente": "Trufa negra", "cantidad": 0.01, "coste_unitario": 180.0}, {"ingrediente": "Parmesano", "cantidad": 0.05, "coste_unitario": 15.0}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>R004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ensalada César</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Entrantes</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>[{"ingrediente": "Lechuga", "cantidad": 0.15, "coste_unitario": 2.0}, {"ingrediente": "Pollo", "cantidad": 0.1, "coste_unitario": 6.5}, {"ingrediente": "Parmesano", "cantidad": 0.03, "coste_unitario": 15.0}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>R005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Tarta Chocolate</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Postres</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>12</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>[{"ingrediente": "Chocolate 70%", "cantidad": 0.08, "coste_unitario": 12.0}, {"ingrediente": "Harina", "cantidad": 0.05, "coste_unitario": 1.0}, {"ingrediente": "Huevo", "cantidad": 0.1, "coste_unitario": 3.0}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>R006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Paella Mixta</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Arroces</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>32</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>[{"ingrediente": "Arroz bomba", "cantidad": 0.12, "coste_unitario": 3.2}, {"ingrediente": "Marisco", "cantidad": 0.15, "coste_unitario": 14.0}, {"ingrediente": "Pollo", "cantidad": 0.1, "coste_unitario": 6.5}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>R007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Sopa de Marisco</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Sopas</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>22</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>[{"ingrediente": "Marisco", "cantidad": 0.2, "coste_unitario": 14.0}, {"ingrediente": "Tomate", "cantidad": 0.1, "coste_unitario": 2.5}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>R008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Hamburguesa Gourmet</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Carnes</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>19</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>[{"ingrediente": "Carne picada", "cantidad": 0.2, "coste_unitario": 9.5}, {"ingrediente": "Pan brioche", "cantidad": 0.08, "coste_unitario": 3.0}, {"ingrediente": "Queso", "cantidad": 0.03, "coste_unitario": 12.0}]</t>
-        </is>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>